--- a/data/trans_bre/IP15-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 0,92</t>
+          <t>-16,09; 0,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 9,76</t>
+          <t>-11,46; 8,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 11,92</t>
+          <t>-9,04; 10,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 10,99</t>
+          <t>-10,09; 10,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,38; 8,06</t>
+          <t>-59,59; 6,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 51,79</t>
+          <t>-39,49; 45,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,81; 89,66</t>
+          <t>-41,58; 81,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,6; 61,86</t>
+          <t>-34,73; 58,3</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 11,01</t>
+          <t>-8,56; 11,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 20,02</t>
+          <t>2,73; 21,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 2,33</t>
+          <t>-12,6; 2,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 11,07</t>
+          <t>-10,32; 11,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 73,52</t>
+          <t>-33,18; 72,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,91; 227,63</t>
+          <t>11,7; 230,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,52; 19,79</t>
+          <t>-60,66; 19,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 59,85</t>
+          <t>-34,63; 60,62</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 4,03</t>
+          <t>-15,28; 5,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 8,09</t>
+          <t>-9,5; 7,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 9,93</t>
+          <t>-8,33; 11,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 4,1</t>
+          <t>-21,6; 4,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 25,74</t>
+          <t>-57,75; 29,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,3; 82,85</t>
+          <t>-50,82; 80,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,99; 111,31</t>
+          <t>-44,97; 127,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 23,08</t>
+          <t>-63,85; 27,73</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 5,55</t>
+          <t>-6,46; 5,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 4,38</t>
+          <t>-9,46; 4,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 10,22</t>
+          <t>-1,68; 10,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 31,46</t>
+          <t>-3,38; 33,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 33,24</t>
+          <t>-30,06; 32,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 19,04</t>
+          <t>-31,91; 19,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 77,47</t>
+          <t>-9,44; 76,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 146,41</t>
+          <t>-13,09; 156,03</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 7,68</t>
+          <t>-8,63; 7,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 6,82</t>
+          <t>-8,64; 7,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 9,5</t>
+          <t>-6,06; 9,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 11,98</t>
+          <t>-6,05; 11,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-41,33; 54,23</t>
+          <t>-38,16; 48,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 44,31</t>
+          <t>-36,58; 46,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,42; 65,84</t>
+          <t>-29,66; 65,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 63,11</t>
+          <t>-22,55; 66,08</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 3,17</t>
+          <t>-14,76; 2,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 4,54</t>
+          <t>-15,85; 5,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 18,22</t>
+          <t>-4,51; 17,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 8,16</t>
+          <t>-16,29; 7,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,24; 37,63</t>
+          <t>-70,57; 32,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,17; 33,31</t>
+          <t>-69,78; 41,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 205,17</t>
+          <t>-25,78; 180,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,7; 58,7</t>
+          <t>-56,66; 50,62</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 0,75</t>
+          <t>-6,12; 0,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 3,67</t>
+          <t>-3,48; 3,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 5,25</t>
+          <t>-1,36; 5,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 13,86</t>
+          <t>-2,65; 13,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 4,15</t>
+          <t>-28,5; 4,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 19,57</t>
+          <t>-15,77; 19,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 36,11</t>
+          <t>-8,04; 35,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 61,72</t>
+          <t>-10,93; 59,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 0,97</t>
+          <t>-17,1; 1,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 8,69</t>
+          <t>-11,75; 8,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 10,63</t>
+          <t>-7,69; 11,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 10,66</t>
+          <t>-8,49; 10,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,59; 6,05</t>
+          <t>-60,42; 7,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,49; 45,69</t>
+          <t>-40,89; 44,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,58; 81,55</t>
+          <t>-35,83; 83,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 58,3</t>
+          <t>-31,46; 56,22</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 11,42</t>
+          <t>-8,74; 11,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 21,25</t>
+          <t>4,12; 21,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 2,2</t>
+          <t>-12,79; 2,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 11,22</t>
+          <t>-10,98; 11,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,18; 72,98</t>
+          <t>-33,03; 80,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,7; 230,5</t>
+          <t>22,5; 261,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,66; 19,79</t>
+          <t>-60,3; 21,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 60,62</t>
+          <t>-35,68; 66,28</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 5,08</t>
+          <t>-14,25; 4,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 7,84</t>
+          <t>-10,14; 7,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 11,08</t>
+          <t>-8,39; 10,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 4,61</t>
+          <t>-23,39; 3,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,75; 29,52</t>
+          <t>-55,62; 24,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 80,03</t>
+          <t>-53,25; 72,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 127,84</t>
+          <t>-46,67; 134,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,85; 27,73</t>
+          <t>-65,46; 21,55</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 5,32</t>
+          <t>-6,17; 6,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 4,37</t>
+          <t>-9,58; 4,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 10,3</t>
+          <t>-1,44; 10,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 33,61</t>
+          <t>-3,47; 35,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 32,57</t>
+          <t>-28,54; 37,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 19,56</t>
+          <t>-32,37; 19,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 76,21</t>
+          <t>-6,97; 84,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 156,03</t>
+          <t>-13,5; 160,17</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 7,54</t>
+          <t>-8,56; 7,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 7,22</t>
+          <t>-8,55; 6,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 9,44</t>
+          <t>-5,89; 10,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 11,89</t>
+          <t>-6,34; 12,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,16; 48,31</t>
+          <t>-38,8; 49,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 46,37</t>
+          <t>-34,93; 38,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 65,84</t>
+          <t>-29,21; 70,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 66,08</t>
+          <t>-24,81; 68,92</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 2,94</t>
+          <t>-14,26; 4,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 5,23</t>
+          <t>-16,03; 4,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 17,48</t>
+          <t>-4,27; 18,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 7,66</t>
+          <t>-14,95; 7,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,57; 32,2</t>
+          <t>-70,44; 59,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,78; 41,11</t>
+          <t>-68,42; 35,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 180,11</t>
+          <t>-22,03; 193,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,66; 50,62</t>
+          <t>-51,61; 50,07</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 0,76</t>
+          <t>-5,95; 0,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,76</t>
+          <t>-3,59; 3,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 5,24</t>
+          <t>-1,59; 5,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 13,15</t>
+          <t>-2,51; 13,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 4,11</t>
+          <t>-27,73; 5,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 19,99</t>
+          <t>-15,67; 19,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 35,41</t>
+          <t>-9,07; 33,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 59,64</t>
+          <t>-10,51; 57,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 1,04</t>
+          <t>-15,83; 0,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 8,78</t>
+          <t>-11,89; 9,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 11,13</t>
+          <t>-8,4; 11,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 10,32</t>
+          <t>-9,21; 10,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 7,38</t>
+          <t>-59,38; 8,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,89; 44,6</t>
+          <t>-39,99; 51,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 83,86</t>
+          <t>-38,81; 89,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 56,22</t>
+          <t>-32,13; 55,3</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>-3,87%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 11,68</t>
+          <t>-8,64; 11,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 21,38</t>
+          <t>2,42; 20,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 2,34</t>
+          <t>-13,4; 2,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 11,85</t>
+          <t>-11,67; 10,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 80,38</t>
+          <t>-35,26; 73,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,5; 261,88</t>
+          <t>12,91; 227,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,3; 21,76</t>
+          <t>-62,52; 19,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 66,28</t>
+          <t>-38,82; 55,42</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-31,69%</t>
+          <t>-32,55%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 4,42</t>
+          <t>-15,63; 4,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 7,15</t>
+          <t>-9,2; 8,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 10,59</t>
+          <t>-8,91; 9,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 3,23</t>
+          <t>-21,05; 3,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,62; 24,84</t>
+          <t>-58,91; 25,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,25; 72,21</t>
+          <t>-50,3; 82,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,67; 134,13</t>
+          <t>-49,99; 111,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,46; 21,55</t>
+          <t>-61,49; 24,66</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,45</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>-3,42%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 6,19</t>
+          <t>-7,05; 5,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 4,4</t>
+          <t>-8,94; 4,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 10,65</t>
+          <t>-1,7; 10,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 35,34</t>
+          <t>-9,41; 6,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 37,17</t>
+          <t>-31,3; 33,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 19,19</t>
+          <t>-30,57; 19,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 84,97</t>
+          <t>-9,44; 77,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 160,17</t>
+          <t>-32,49; 32,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 7,38</t>
+          <t>-9,22; 7,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 6,08</t>
+          <t>-8,82; 6,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 10,01</t>
+          <t>-6,08; 9,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 12,07</t>
+          <t>-6,88; 11,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 49,54</t>
+          <t>-41,33; 54,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 38,92</t>
+          <t>-36,22; 44,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 70,72</t>
+          <t>-28,42; 65,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 68,92</t>
+          <t>-25,41; 61,2</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-16,51%</t>
+          <t>-14,39%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 4,97</t>
+          <t>-14,38; 3,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 4,98</t>
+          <t>-15,06; 4,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 18,35</t>
+          <t>-3,78; 18,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 7,34</t>
+          <t>-14,6; 8,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,44; 59,02</t>
+          <t>-70,24; 37,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 35,83</t>
+          <t>-69,17; 33,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 193,52</t>
+          <t>-22,61; 205,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,61; 50,07</t>
+          <t>-54,38; 68,15</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>-0,9</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>-3,8%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 0,93</t>
+          <t>-5,83; 0,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 3,68</t>
+          <t>-3,79; 3,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,06</t>
+          <t>-1,31; 5,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 13,49</t>
+          <t>-4,7; 3,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 5,72</t>
+          <t>-26,47; 4,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 19,11</t>
+          <t>-17,05; 19,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 33,0</t>
+          <t>-7,04; 36,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 57,68</t>
+          <t>-18,57; 16,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-7,46</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-33,92%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-5,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-7.463666503631525</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.420248866081575</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.287204624656621</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.2904056729620241</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.3392237687060751</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.05754099159180191</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.07239601999515791</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.01228080863790226</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-15,83; 0,92</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-11,89; 9,76</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-8,4; 11,92</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-9,21; 10,28</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-59,38; 8,06</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-39,99; 51,79</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-38,81; 89,66</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-32,13; 55,3</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-15.83198110725563</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-11.89364222010034</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-8.396445759966172</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-9.211551059356818</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5937884996974059</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3999427540880691</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3880574906462204</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3212945632447973</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9161757584657817</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.760389751654783</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.92221850744115</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.2798768292416</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.08062609276261808</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.517940191809126</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.8966451032742954</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.5529799360276082</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12,07</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-5,56</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-32,88%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-3,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,64; 11,01</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,42; 20,02</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-13,4; 2,33</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,67; 10,12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-35,26; 73,52</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,91; 227,63</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-62,52; 19,79</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-38,82; 55,42</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.462273135950654</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>12.06633855897299</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-5.559198469923951</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.9581773115085013</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.0703976679291279</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.9660276536346241</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3288189401392758</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.03870508689678815</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,61</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-8,59</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-25,4%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-7,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-32,55%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.639202386420115</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2.42394039832952</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-13.39996947545387</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.67032890661605</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3525999054228164</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.1291460226768344</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6252498298937641</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3881690441211762</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-15,63; 4,03</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,2; 8,09</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,91; 9,93</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-21,05; 3,82</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-58,91; 25,74</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-50,3; 82,85</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-49,99; 111,31</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-61,49; 24,66</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>11.00941876899073</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>20.01516171870096</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.32725747807982</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10.11851394673326</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.7351519136961761</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.276264003427857</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.1978837046052665</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.5541605230281451</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,42</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-8,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-3,42%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.614426363093291</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.047346828082454</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6937034347673621</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-8.589503146532627</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2540495564699844</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.07293001712416936</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.05096589068632848</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.3255186583567989</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-7,05; 5,55</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,94; 4,38</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,7; 10,22</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-9,41; 6,86</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-31,3; 33,24</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-30,57; 19,04</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-9,44; 77,47</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-32,49; 32,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-15.63381957343867</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-9.198789589863761</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.908633847232942</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-21.05292777513886</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5891189128192373</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5030333596229339</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4998646589303765</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6148915004163853</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.030824408081885</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.090958990584756</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.925020031663752</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.822757621327763</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2573836150125414</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.8285381084260941</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.113096473137399</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.2466086307564244</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-3,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-9,22; 7,68</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-8,82; 6,82</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,08; 9,5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-6,88; 11,21</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-41,33; 54,23</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-36,22; 44,31</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-28,42; 65,84</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-25,41; 61,2</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.4217025675950309</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.225048032312238</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4.419930499462957</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.8425316010120087</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02196876026240839</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.08615648972080392</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2699459250044157</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.03420367902596587</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-5,66</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-5,74</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6,91</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-2,98</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-36,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-30,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>47,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-14,39%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-7.046947607519138</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.937891631168839</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.699101639210066</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-9.413012125186745</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3130082887627834</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3056845370615158</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.09441750428820374</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3249131259492841</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-14,38; 3,17</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-15,06; 4,54</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-3,78; 18,22</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-14,6; 8,33</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-70,24; 37,63</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-69,17; 33,31</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-22,61; 205,17</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-54,38; 68,15</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.554773641176984</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.375848105354065</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.21659615354913</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.863213604012526</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.332353574293243</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1904219318694974</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.774716571595076</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3254253676286244</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-2,59</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-13,09%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,08%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-3,8%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.6679055292849623</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.6733578265477214</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.612018768264436</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.57626484819522</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.03557364200209631</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.03387747025686885</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.0898857470400482</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.1187162920589233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-5,83; 0,75</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,79; 3,67</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,31; 5,25</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-4,7; 3,62</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-26,47; 4,15</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-17,05; 19,57</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-7,04; 36,11</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-18,57; 16,56</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-9.222756991190098</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-8.822659584730847</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.080007352180259</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-6.879922578072768</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4133078965536067</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3621996636063555</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2841650261594475</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2541160180564044</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.683779780018174</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.815383501350992</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.502510744231122</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>11.20729585595862</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.5423239462276509</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.4431139412914962</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.6584363893926605</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.6120436123031686</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-5.6644504900052</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-5.741912135967553</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>6.905890511906579</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-2.975090588582599</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3617090626287091</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.3049301547731826</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.4790280620806668</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.1439350412743396</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-14.38026893558907</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-15.05601258691887</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-3.784928076870206</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-14.59845991374106</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.7023771262674583</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6917032271986934</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.226080805770048</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.5438262688143465</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3.172088189187743</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4.536784306554019</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>18.22201661681331</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>8.333563611573036</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.3762946274610061</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.3330770464421269</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2.051741302491299</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.681468336604663</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-2.586205978933847</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.01655135397382324</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.800340397631514</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.895935618685062</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.1308624922871647</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.00080363562365738</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.1091779877145933</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.03797029174390992</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-5.83342926572748</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.78874875000576</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.305991203165053</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-4.703659059138674</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.264741232308785</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.1705346447111314</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.07035196235057539</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.1857470765753071</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.747378612761772</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.670798432037373</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>5.250562035360236</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.61541068436246</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.041519839910484</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.1956988265384249</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.3610811048601871</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.1656259779812588</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
